--- a/حركات قديمة موحد الاصح للاستيراد.xlsx
+++ b/حركات قديمة موحد الاصح للاستيراد.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Omar\waad_temp_website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845D4008-93E5-405A-8119-5815D01676AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28D50EE-92AA-43EF-86BA-8E1C04B7C436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="موحد بدون تكرار" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'موحد بدون تكرار'!$A$1:$E$3322</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -76767,6 +76770,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E3322" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>